--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.39142859132849</v>
+        <v>4.126107146090879</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22958703871582</v>
+        <v>4.099807893791321</v>
       </c>
       <c r="E2" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F2" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.23278287197154</v>
+        <v>4.425327216695376</v>
       </c>
       <c r="D3" t="n">
-        <v>26.74899446684456</v>
+        <v>4.346711600862242</v>
       </c>
       <c r="E3" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F3" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.51331772339192</v>
+        <v>7.395914130051187</v>
       </c>
       <c r="D4" t="n">
-        <v>46.90023095133217</v>
+        <v>7.621287529591478</v>
       </c>
       <c r="E4" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F4" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.45380366846024</v>
+        <v>2.836243096124788</v>
       </c>
       <c r="D5" t="n">
-        <v>61.3451823385923</v>
+        <v>9.96859213002125</v>
       </c>
       <c r="E5" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F5" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.28790833564932</v>
+        <v>4.921785104543015</v>
       </c>
       <c r="D6" t="n">
-        <v>72.31958504175128</v>
+        <v>11.75193256928458</v>
       </c>
       <c r="E6" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F6" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.23841075719295</v>
+        <v>4.913741748043854</v>
       </c>
       <c r="D7" t="n">
-        <v>28.99676773086698</v>
+        <v>4.711974756265884</v>
       </c>
       <c r="E7" t="n">
-        <v>8.412234312182099</v>
+        <v>1.366988075729591</v>
       </c>
       <c r="F7" t="n">
-        <v>18.19010649142564</v>
+        <v>2.955892304856667</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
